--- a/output/2026-09-20_11_Croazia_Vukovarsko-srijemska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_11_Croazia_Vukovarsko-srijemska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sede legale a Zagabria (Mirka Viriusa 2); punto vendita a Vukovar (Ul. Kriva Bara 1) attivo dal 2015, confermato da fonti indipendenti.</t>
+          <t>Sede legale a Zagabria (Mirka Viriusa 2); punto vendita a Vukovar (Ul. Kriva Bara 1) attivo dal 2015, confermato da fonti indipendenti. [DUPLICATO — vedi anche: 2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Attiva dal 1995, 312 dipendenti, fatturato 2025 ~36,67 mln €. Attività confermata su registri camerali. Filiale Vukovar citata ma non confermata autonomamente in fonti indipendenti.</t>
+          <t>Attiva dal 1995, 312 dipendenti, fatturato 2025 ~36,67 mln €. Attività confermata su registri camerali. Filiale Vukovar citata ma non confermata autonomamente in fonti indipendenti. [DUPLICATO — vedi anche: 2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Registrata dal 2018 (attività dal 2002 come ditta artigiana), 19 dipendenti, rating creditizio AA+. Confermata distributrice ufficiale Messer per la Vukovarsko-srijemska županija.</t>
+          <t>Registrata dal 2018 (attività dal 2002 come ditta artigiana), 19 dipendenti, rating creditizio AA+. Confermata distributrice ufficiale Messer per la Vukovarsko-srijemska županija. [DUPLICATO — vedi anche: 2026-09-20_06_Croazia_Vukovarsko-srijemska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Due punti vendita confermati a Vinkovci (Ul. Hansa Dietricha Genschera 40 e Ul. Hrvatskih kraljeva 11a).</t>
+          <t>Due punti vendita confermati a Vinkovci (Ul. Hansa Dietricha Genschera 40 e Ul. Hrvatskih kraljeva 11a). [DUPLICATO — vedi anche: 2026-09-20_06_Croazia_Vukovarsko-srijemska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fondata nel 1992; importatore/distributore ufficiale per la Croazia di più marchi internazionali; presenza in tutta la Slavonia.</t>
+          <t>Fondata nel 1992; importatore/distributore ufficiale per la Croazia di più marchi internazionali; presenza in tutta la Slavonia. [DUPLICATO — vedi anche: 2026-09-20_06_Croazia_Vukovarsko-srijemska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fondata nel 1993, rappresentante autorizzato di numerosi marchi internazionali.</t>
+          <t>Fondata nel 1993, rappresentante autorizzato di numerosi marchi internazionali. [DUPLICATO — vedi anche: 2026-09-20_10_Croazia_Vukovarsko-srijemska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oltre 60 anni di attività, indirizzo Bana Jelačića 166, Vinkovci. Attività mista vendita+assistenza; mantenuta perché rivende prodotti di terzi (non cliente finale del settore metalworking). Email integrata da fonte indipendente (non presente nella lista grezza originale).</t>
+          <t>Oltre 60 anni di attività, indirizzo Bana Jelačića 166, Vinkovci. Attività mista vendita+assistenza; mantenuta perché rivende prodotti di terzi (non cliente finale del settore metalworking). Email integrata da fonte indipendente (non presente nella lista grezza originale). [DUPLICATO — vedi anche: 2026-09-20_06_Croazia_Vukovarsko-srijemska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Catena nazionale, punto vendita confermato Ul. Hansa Dietricha Genschera 135, Vinkovci.</t>
+          <t>Catena nazionale, punto vendita confermato Ul. Hansa Dietricha Genschera 135, Vinkovci. [DUPLICATO — vedi anche: 2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -779,7 +779,6 @@
           <t>Grande distribuzione ferramenta/bricolage: utensili, saldatrici, elettrodi, compressori, DPI</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Stessa catena della riga precedente, punto vendita distinto confermato in Kudeljarska ul. 4A, Vukovar. Telefono/email specifici del punto vendita non reperiti.</t>
@@ -812,7 +811,6 @@
           <t>Distributore abbigliamento da lavoro e DPI per industria</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Filiale di Vinkovci confermata (centro commerciale "Matice") ma indirizzo civico e contatti diretti della filiale non reperibili in fonti indipendenti; numero della sede centrale di Čazma non usato per policy anti-invenzione dati.</t>

--- a/output/2026-09-20_11_Croazia_Vukovarsko-srijemska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_11_Croazia_Vukovarsko-srijemska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-20_11_Croazia_Vukovarsko-srijemska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_11_Croazia_Vukovarsko-srijemska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stessa catena della riga precedente, punto vendita distinto confermato in Kudeljarska ul. 4A, Vukovar. Telefono/email specifici del punto vendita non reperiti.</t>
+          <t>Stessa catena della riga precedente, punto vendita distinto confermato in Kudeljarska ul. 4A, Vukovar. Telefono/email specifici del punto vendita non reperiti. [DUPLICATO — vedi anche: 2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
